--- a/InputData/trans/PVTStL/Policy Veh Types Subject to LCFS.xlsx
+++ b/InputData/trans/PVTStL/Policy Veh Types Subject to LCFS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\PVTStL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\trans\PVTStL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8B7640-3F18-4F5C-A9FF-A8B089B6F820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D9DDAF-76D6-41CF-A17D-78ADD389977F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21120" windowHeight="14760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Source:</t>
   </si>
@@ -80,10 +80,13 @@
     <t>(Boolean)</t>
   </si>
   <si>
-    <t>Based on the California LCFS, we choose to exempt aircraft.</t>
-  </si>
-  <si>
     <t>PVTStL Policy Vehicle Types Subject to LCFS</t>
+  </si>
+  <si>
+    <t>We configure this file to apply only to aviation and shipping in order to represent</t>
+  </si>
+  <si>
+    <t>policy support for sustainable aviation and shipping fuel.</t>
   </si>
 </sst>
 </file>
@@ -440,12 +443,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -503,7 +506,12 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -541,10 +549,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -552,10 +560,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
